--- a/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
+++ b/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="1" r:id="R70ea6d58ae0e4c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景矩阵" sheetId="2" r:id="R5b3b5ac82ec142cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="R71697897c9bd44e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="R54201223260443bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="Rb7c224934772443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="R2d1a885bdace42b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="Rd3a51857692b4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="R48dd4f2dade8426f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,43 +180,51 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DispenserSceneMatrix" displayName="DispenserSceneMatrix" ref="A3:T6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="20">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DispenserVideoStrategy" displayName="DispenserVideoStrategy" ref="A3:AA6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="27">
     <x:tableColumn id="1" name="案例ID"/>
     <x:tableColumn id="2" name="案例名称"/>
-    <x:tableColumn id="3" name="唯一组合指纹"/>
-    <x:tableColumn id="4" name="物体种类"/>
-    <x:tableColumn id="5" name="物体形态"/>
-    <x:tableColumn id="6" name="环境场景"/>
-    <x:tableColumn id="7" name="覆盖状态"/>
-    <x:tableColumn id="8" name="镜头景别"/>
-    <x:tableColumn id="9" name="镜头运动"/>
-    <x:tableColumn id="10" name="人物/施工状态"/>
-    <x:tableColumn id="11" name="首帧状态"/>
-    <x:tableColumn id="12" name="视频状态"/>
-    <x:tableColumn id="13" name="图片哈希"/>
-    <x:tableColumn id="14" name="视频哈希"/>
-    <x:tableColumn id="15" name="图片模型"/>
-    <x:tableColumn id="16" name="视频模型"/>
-    <x:tableColumn id="17" name="预计视频费用（元）"/>
-    <x:tableColumn id="18" name="生成秒数"/>
-    <x:tableColumn id="19" name="任务状态"/>
-    <x:tableColumn id="20" name="项目相对路径"/>
+    <x:tableColumn id="3" name="物体种类"/>
+    <x:tableColumn id="4" name="物体形态"/>
+    <x:tableColumn id="5" name="环境场景"/>
+    <x:tableColumn id="6" name="覆盖状态"/>
+    <x:tableColumn id="7" name="镜头景别"/>
+    <x:tableColumn id="8" name="镜头运动"/>
+    <x:tableColumn id="9" name="人物/施工状态"/>
+    <x:tableColumn id="10" name="完整文生视频提示词"/>
+    <x:tableColumn id="11" name="图生视频提示词"/>
+    <x:tableColumn id="12" name="首帧提示词"/>
+    <x:tableColumn id="13" name="负面提示词"/>
+    <x:tableColumn id="14" name="唯一组合指纹"/>
+    <x:tableColumn id="15" name="首帧状态"/>
+    <x:tableColumn id="16" name="视频状态"/>
+    <x:tableColumn id="17" name="图片哈希"/>
+    <x:tableColumn id="18" name="视频哈希"/>
+    <x:tableColumn id="19" name="图片模型"/>
+    <x:tableColumn id="20" name="视频模型"/>
+    <x:tableColumn id="21" name="预计视频费用（元）"/>
+    <x:tableColumn id="22" name="生成秒数"/>
+    <x:tableColumn id="23" name="任务状态"/>
+    <x:tableColumn id="24" name="参考图片"/>
+    <x:tableColumn id="25" name="项目相对路径"/>
+    <x:tableColumn id="26" name="文生视频提示词哈希"/>
+    <x:tableColumn id="27" name="图生视频提示词哈希"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DispenserPromptArchive" displayName="DispenserPromptArchive" ref="A3:G6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DispenserPromptArchive" displayName="DispenserPromptArchive" ref="A3:H6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
     <x:tableColumn id="1" name="案例ID"/>
-    <x:tableColumn id="2" name="首帧提示词"/>
-    <x:tableColumn id="3" name="视频提示词"/>
-    <x:tableColumn id="4" name="负面提示词"/>
-    <x:tableColumn id="5" name="参考图片"/>
-    <x:tableColumn id="6" name="首帧提示词哈希"/>
-    <x:tableColumn id="7" name="视频提示词哈希"/>
+    <x:tableColumn id="2" name="完整文生视频提示词"/>
+    <x:tableColumn id="3" name="图生视频提示词"/>
+    <x:tableColumn id="4" name="首帧提示词"/>
+    <x:tableColumn id="5" name="负面提示词"/>
+    <x:tableColumn id="6" name="参考图片"/>
+    <x:tableColumn id="7" name="文生视频提示词哈希"/>
+    <x:tableColumn id="8" name="图生视频提示词哈希"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -429,6 +437,470 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="70" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="70" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="70" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="70" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="16" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="16" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="34" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="38" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="16" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="K1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="N1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="O1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="P1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="Q1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="R1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="S1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="T1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="U1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="V1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="W1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="X1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="Y1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="Z1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+      <x:c r="AA1" s="3" t="str">
+        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="10" t="str">
+        <x:v>案例ID</x:v>
+      </x:c>
+      <x:c r="B3" s="15" t="str">
+        <x:v>案例名称</x:v>
+      </x:c>
+      <x:c r="C3" s="15" t="str">
+        <x:v>物体种类</x:v>
+      </x:c>
+      <x:c r="D3" s="15" t="str">
+        <x:v>物体形态</x:v>
+      </x:c>
+      <x:c r="E3" s="15" t="str">
+        <x:v>环境场景</x:v>
+      </x:c>
+      <x:c r="F3" s="15" t="str">
+        <x:v>覆盖状态</x:v>
+      </x:c>
+      <x:c r="G3" s="15" t="str">
+        <x:v>镜头景别</x:v>
+      </x:c>
+      <x:c r="H3" s="15" t="str">
+        <x:v>镜头运动</x:v>
+      </x:c>
+      <x:c r="I3" s="15" t="str">
+        <x:v>人物/施工状态</x:v>
+      </x:c>
+      <x:c r="J3" s="15" t="str">
+        <x:v>完整文生视频提示词</x:v>
+      </x:c>
+      <x:c r="K3" s="15" t="str">
+        <x:v>图生视频提示词</x:v>
+      </x:c>
+      <x:c r="L3" s="15" t="str">
+        <x:v>首帧提示词</x:v>
+      </x:c>
+      <x:c r="M3" s="15" t="str">
+        <x:v>负面提示词</x:v>
+      </x:c>
+      <x:c r="N3" s="15" t="str">
+        <x:v>唯一组合指纹</x:v>
+      </x:c>
+      <x:c r="O3" s="15" t="str">
+        <x:v>首帧状态</x:v>
+      </x:c>
+      <x:c r="P3" s="15" t="str">
+        <x:v>视频状态</x:v>
+      </x:c>
+      <x:c r="Q3" s="15" t="str">
+        <x:v>图片哈希</x:v>
+      </x:c>
+      <x:c r="R3" s="15" t="str">
+        <x:v>视频哈希</x:v>
+      </x:c>
+      <x:c r="S3" s="15" t="str">
+        <x:v>图片模型</x:v>
+      </x:c>
+      <x:c r="T3" s="15" t="str">
+        <x:v>视频模型</x:v>
+      </x:c>
+      <x:c r="U3" s="15" t="str">
+        <x:v>预计视频费用（元）</x:v>
+      </x:c>
+      <x:c r="V3" s="15" t="str">
+        <x:v>生成秒数</x:v>
+      </x:c>
+      <x:c r="W3" s="15" t="str">
+        <x:v>任务状态</x:v>
+      </x:c>
+      <x:c r="X3" s="15" t="str">
+        <x:v>参考图片</x:v>
+      </x:c>
+      <x:c r="Y3" s="15" t="str">
+        <x:v>项目相对路径</x:v>
+      </x:c>
+      <x:c r="Z3" s="15" t="str">
+        <x:v>文生视频提示词哈希</x:v>
+      </x:c>
+      <x:c r="AA3" s="11" t="str">
+        <x:v>图生视频提示词哈希</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="300" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>v01-s01</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>饮水机案例01</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>water dispenser</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>tall narrow floor-standing white dispenser</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>cool modern office break room</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>fully covered to the floor by a straight clear curtain</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>symmetrical full-body shot</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
+        <x:v>slow right-to-left lateral slider</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>no person; completed protection state</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
+        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: tall narrow floor-standing white dispenser. Environment: cool modern office break room. Coverage state: fully covered to the floor by a straight clear curtain. Shot scale: symmetrical full-body shot. Camera motion: slow right-to-left lateral slider. Person or work state: no person; completed protection state. Opening visual and product geometry: Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="K4" s="16" t="str">
+        <x:v>Preserve the cool office break room, tall narrow dispenser and approved intact tape-film geometry. Use a slow right-to-left lateral slider with mild background parallax. The single transparent curtain remains fully connected to the yellow tape and covers the complete dispenser down to the floor. Only fine surface shimmer is allowed. No person enters; no water flow, tear, split, extra tape, duplicate layer, exposed dispenser, installation, transformation, text or logo.</x:v>
+      </x:c>
+      <x:c r="L4" s="16" t="str">
+        <x:v>Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="M4" s="16" t="str">
+        <x:v>broken plastic, tape wider than film, second tape, uncovered dispenser, water flow</x:v>
+      </x:c>
+      <x:c r="N4" s="16" t="str">
+        <x:v>0a02369494b1</x:v>
+      </x:c>
+      <x:c r="O4" s="16" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="P4" s="16" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="Q4" s="16" t="str">
+        <x:v>13e513264b9feae344fecb4235e667fcb411f01f54ecf1351d125ff44088771a</x:v>
+      </x:c>
+      <x:c r="R4" s="16" t="str">
+        <x:v>3e301610ebab3909b68f7fe3e911362108008c94e1075cbef0bc5533860ae005</x:v>
+      </x:c>
+      <x:c r="S4" s="16" t="str">
+        <x:v>seedream-5.0-lite</x:v>
+      </x:c>
+      <x:c r="T4" s="16" t="str">
+        <x:v>grok-imagine-video-1.5-fast</x:v>
+      </x:c>
+      <x:c r="U4" s="20" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="V4" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="W4" s="16" t="str">
+        <x:v>completed</x:v>
+      </x:c>
+      <x:c r="X4" s="16" t="str">
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
+      </x:c>
+      <x:c r="Y4" s="16" t="str">
+        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
+      </x:c>
+      <x:c r="Z4" s="16" t="str">
+        <x:v>0dd1729bd3ffc618</x:v>
+      </x:c>
+      <x:c r="AA4" s="16" t="str">
+        <x:v>d8d6757fea280462</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="300" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>v02-s01</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>饮水机案例02</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>water dispenser</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>compact countertop dispenser</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>small renovated apartment kitchen</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="str">
+        <x:v>fully covered from wall tape to below the countertop front edge</x:v>
+      </x:c>
+      <x:c r="G5" s="16" t="str">
+        <x:v>three-quarter medium-close shot</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="str">
+        <x:v>slow forward push-in</x:v>
+      </x:c>
+      <x:c r="I5" s="16" t="str">
+        <x:v>painter standing at frame left inspecting the tape line without contact</x:v>
+      </x:c>
+      <x:c r="J5" s="16" t="str">
+        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: compact countertop dispenser. Environment: small renovated apartment kitchen. Coverage state: fully covered from wall tape to below the countertop front edge. Shot scale: three-quarter medium-close shot. Camera motion: slow forward push-in. Person or work state: painter standing at frame left inspecting the tape line without contact. Opening visual and product geometry: Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="K5" s="16" t="str">
+        <x:v>Keep the renovated apartment kitchen, compact countertop dispenser, painter and approved continuous tape-film structure unchanged. Perform a slow forward push-in toward the protected appliance. The painter briefly looks from the yellow tape line to the covered counter and remains still without contact. The single clear sheet stays connected endpoint-to-endpoint and continues below the counter edge; the entire dispenser remains behind it. No rip, second layer, extra tape, hand contact, water flow, exposed surface, speech, text or logo.</x:v>
+      </x:c>
+      <x:c r="L5" s="16" t="str">
+        <x:v>Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="M5" s="16" t="str">
+        <x:v>floor-standing appliance, torn film, hands touching tape, duplicate tape, uncovered counter</x:v>
+      </x:c>
+      <x:c r="N5" s="16" t="str">
+        <x:v>c2a061a328a2</x:v>
+      </x:c>
+      <x:c r="O5" s="16" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="P5" s="16" t="str">
+        <x:v>淘汰</x:v>
+      </x:c>
+      <x:c r="Q5" s="16" t="str">
+        <x:v>f39260f4b7ce3f28bef5b2b29c23c7c2665d02c37487296fb3f48458ba1b54b4</x:v>
+      </x:c>
+      <x:c r="R5" s="16" t="str">
+        <x:v>53a6060201822c1748a08412275ff581c74b6bf91e892631eda658b31399a2a2</x:v>
+      </x:c>
+      <x:c r="S5" s="16" t="str">
+        <x:v>seedream-5.0-lite</x:v>
+      </x:c>
+      <x:c r="T5" s="16" t="str">
+        <x:v>grok-imagine-video-1.5-fast</x:v>
+      </x:c>
+      <x:c r="U5" s="20" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="V5" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="W5" s="16" t="str">
+        <x:v>completed</x:v>
+      </x:c>
+      <x:c r="X5" s="16" t="str">
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
+      </x:c>
+      <x:c r="Y5" s="16" t="str">
+        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
+      </x:c>
+      <x:c r="Z5" s="16" t="str">
+        <x:v>66c7b936edb6b438</x:v>
+      </x:c>
+      <x:c r="AA5" s="16" t="str">
+        <x:v>6bf77b8c6030df84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="300" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>v03-s01</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>饮水机案例03</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>water dispenser</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>wide black-and-silver bottom-loading floor dispenser</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>clean clinic corridor renovation zone</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="str">
+        <x:v>fully covered with broad side margins and gathered floor edge</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="str">
+        <x:v>low-angle wide environmental shot</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
+        <x:v>gentle upward pedestal move</x:v>
+      </x:c>
+      <x:c r="I6" s="16" t="str">
+        <x:v>worker standing at frame right presenting the protected appliance</x:v>
+      </x:c>
+      <x:c r="J6" s="16" t="str">
+        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: wide black-and-silver bottom-loading floor dispenser. Environment: clean clinic corridor renovation zone. Coverage state: fully covered with broad side margins and gathered floor edge. Shot scale: low-angle wide environmental shot. Camera motion: gentle upward pedestal move. Person or work state: worker standing at frame right presenting the protected appliance. Opening visual and product geometry: Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="K6" s="16" t="str">
+        <x:v>Preserve the clinic corridor, wide bottom-loading dispenser, standing worker and exact one-piece tape-film installation. Use a gentle upward pedestal move from the gathered floor edge to the yellow tape line. The worker makes one small open-palm presentation gesture beside the covered appliance. The broad transparent sheet remains a single continuous layer with full side margins and stable endpoint alignment. No tear, second flap, loose tape, water flow, contact, uncovered cabinet, camera orbit, speech, text or logo.</x:v>
+      </x:c>
+      <x:c r="L6" s="16" t="str">
+        <x:v>Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="M6" s="16" t="str">
+        <x:v>narrow dispenser, ripped film, extra tape, presenter occlusion, open cabinet, water stream</x:v>
+      </x:c>
+      <x:c r="N6" s="16" t="str">
+        <x:v>bd6fe4d687c8</x:v>
+      </x:c>
+      <x:c r="O6" s="16" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="P6" s="16" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="Q6" s="16" t="str">
+        <x:v>77797f056a034f2138e9d0464cc38c4f819d7f8f085291535f66d1fbf0d2b1e4</x:v>
+      </x:c>
+      <x:c r="R6" s="16" t="str">
+        <x:v>0f2381b762c8a7018817fe4d7de4378b081a6f106177bbcbfa1dfa46f7b51262</x:v>
+      </x:c>
+      <x:c r="S6" s="16" t="str">
+        <x:v>seedream-5.0-lite</x:v>
+      </x:c>
+      <x:c r="T6" s="16" t="str">
+        <x:v>grok-imagine-video-1.5-fast</x:v>
+      </x:c>
+      <x:c r="U6" s="20" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="V6" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="W6" s="16" t="str">
+        <x:v>completed</x:v>
+      </x:c>
+      <x:c r="X6" s="16" t="str">
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
+      </x:c>
+      <x:c r="Y6" s="16" t="str">
+        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
+      </x:c>
+      <x:c r="Z6" s="16" t="str">
+        <x:v>591522cb439878e4</x:v>
+      </x:c>
+      <x:c r="AA6" s="16" t="str">
+        <x:v>f5c62dc3f4529607</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:AA1"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="O4:P6">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="淘汰"/>
+    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="待"/>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57415b5bfe6b402b"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
@@ -482,7 +954,7 @@
         <x:v>差异化案例数</x:v>
       </x:c>
       <x:c r="B4" s="17" t="n">
-        <x:f>COUNTA('场景矩阵'!$A$4:$A$100)</x:f>
+        <x:f>COUNTA('视频策略库'!$A$4:$A$100)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="17"/>
@@ -495,7 +967,7 @@
         <x:v>唯一七维组合数</x:v>
       </x:c>
       <x:c r="B5" s="17" t="n">
-        <x:f>COUNTA('场景矩阵'!$C$4:$C$100)</x:f>
+        <x:f>COUNTA('视频策略库'!$N$4:$N$100)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="17"/>
@@ -508,7 +980,7 @@
         <x:v>首帧通过数</x:v>
       </x:c>
       <x:c r="B6" s="17" t="n">
-        <x:f>COUNTIF('场景矩阵'!$K$4:$K$100,"通过")</x:f>
+        <x:f>COUNTIF('视频策略库'!$O$4:$O$100,"通过")</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="17"/>
@@ -521,7 +993,7 @@
         <x:v>视频通过数</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
-        <x:f>COUNTIF('场景矩阵'!$L$4:$L$100,"通过")</x:f>
+        <x:f>COUNTIF('视频策略库'!$P$4:$P$100,"通过")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="17"/>
@@ -534,7 +1006,7 @@
         <x:v>预计视频费用（元）</x:v>
       </x:c>
       <x:c r="B8" s="18" t="n">
-        <x:f>ROUND(SUM('场景矩阵'!$Q$4:$Q$100),2)</x:f>
+        <x:f>ROUND(SUM('视频策略库'!$U$4:$U$100),2)</x:f>
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="C8" s="17"/>
@@ -577,7 +1049,7 @@
         <x:v>台账定位</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>用于筛选策略、查看提示词、追踪验收与复盘淘汰素材</x:v>
+        <x:v>主表逐行列出七维组合及其完整文生视频提示词；统计页仅用于辅助查看</x:v>
       </x:c>
       <x:c r="C12" s="19"/>
       <x:c r="D12" s="19"/>
@@ -608,392 +1080,44 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="34" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="M1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="N1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="O1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="P1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="Q1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="R1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="S1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-      <x:c r="T1" s="3" t="str">
-        <x:v>饮水机场景矩阵｜七维组合与生产状态</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="10" t="str">
-        <x:v>案例ID</x:v>
-      </x:c>
-      <x:c r="B3" s="15" t="str">
-        <x:v>案例名称</x:v>
-      </x:c>
-      <x:c r="C3" s="15" t="str">
-        <x:v>唯一组合指纹</x:v>
-      </x:c>
-      <x:c r="D3" s="15" t="str">
-        <x:v>物体种类</x:v>
-      </x:c>
-      <x:c r="E3" s="15" t="str">
-        <x:v>物体形态</x:v>
-      </x:c>
-      <x:c r="F3" s="15" t="str">
-        <x:v>环境场景</x:v>
-      </x:c>
-      <x:c r="G3" s="15" t="str">
-        <x:v>覆盖状态</x:v>
-      </x:c>
-      <x:c r="H3" s="15" t="str">
-        <x:v>镜头景别</x:v>
-      </x:c>
-      <x:c r="I3" s="15" t="str">
-        <x:v>镜头运动</x:v>
-      </x:c>
-      <x:c r="J3" s="15" t="str">
-        <x:v>人物/施工状态</x:v>
-      </x:c>
-      <x:c r="K3" s="15" t="str">
-        <x:v>首帧状态</x:v>
-      </x:c>
-      <x:c r="L3" s="15" t="str">
-        <x:v>视频状态</x:v>
-      </x:c>
-      <x:c r="M3" s="15" t="str">
-        <x:v>图片哈希</x:v>
-      </x:c>
-      <x:c r="N3" s="15" t="str">
-        <x:v>视频哈希</x:v>
-      </x:c>
-      <x:c r="O3" s="15" t="str">
-        <x:v>图片模型</x:v>
-      </x:c>
-      <x:c r="P3" s="15" t="str">
-        <x:v>视频模型</x:v>
-      </x:c>
-      <x:c r="Q3" s="15" t="str">
-        <x:v>预计视频费用（元）</x:v>
-      </x:c>
-      <x:c r="R3" s="15" t="str">
-        <x:v>生成秒数</x:v>
-      </x:c>
-      <x:c r="S3" s="15" t="str">
-        <x:v>任务状态</x:v>
-      </x:c>
-      <x:c r="T3" s="11" t="str">
-        <x:v>项目相对路径</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="16" t="str">
-        <x:v>v01-s01</x:v>
-      </x:c>
-      <x:c r="B4" s="16" t="str">
-        <x:v>饮水机案例01</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="str">
-        <x:v>0a02369494b1</x:v>
-      </x:c>
-      <x:c r="D4" s="16" t="str">
-        <x:v>water dispenser</x:v>
-      </x:c>
-      <x:c r="E4" s="16" t="str">
-        <x:v>tall narrow floor-standing white dispenser</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="str">
-        <x:v>cool modern office break room</x:v>
-      </x:c>
-      <x:c r="G4" s="16" t="str">
-        <x:v>fully covered to the floor by a straight clear curtain</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="str">
-        <x:v>symmetrical full-body shot</x:v>
-      </x:c>
-      <x:c r="I4" s="16" t="str">
-        <x:v>slow right-to-left lateral slider</x:v>
-      </x:c>
-      <x:c r="J4" s="16" t="str">
-        <x:v>no person; completed protection state</x:v>
-      </x:c>
-      <x:c r="K4" s="16" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="L4" s="16" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="M4" s="16" t="str">
-        <x:v>13e513264b9feae344fecb4235e667fcb411f01f54ecf1351d125ff44088771a</x:v>
-      </x:c>
-      <x:c r="N4" s="16" t="str">
-        <x:v>3e301610ebab3909b68f7fe3e911362108008c94e1075cbef0bc5533860ae005</x:v>
-      </x:c>
-      <x:c r="O4" s="16" t="str">
-        <x:v>seedream-5.0-lite</x:v>
-      </x:c>
-      <x:c r="P4" s="16" t="str">
-        <x:v>grok-imagine-video-1.5-fast</x:v>
-      </x:c>
-      <x:c r="Q4" s="20" t="n">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="R4" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S4" s="16" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="T4" s="16" t="str">
-        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="16" t="str">
-        <x:v>v02-s01</x:v>
-      </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>饮水机案例02</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
-        <x:v>c2a061a328a2</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>water dispenser</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>compact countertop dispenser</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>small renovated apartment kitchen</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
-        <x:v>fully covered from wall tape to below the countertop front edge</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="str">
-        <x:v>three-quarter medium-close shot</x:v>
-      </x:c>
-      <x:c r="I5" s="16" t="str">
-        <x:v>slow forward push-in</x:v>
-      </x:c>
-      <x:c r="J5" s="16" t="str">
-        <x:v>painter standing at frame left inspecting the tape line without contact</x:v>
-      </x:c>
-      <x:c r="K5" s="16" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="L5" s="16" t="str">
-        <x:v>淘汰</x:v>
-      </x:c>
-      <x:c r="M5" s="16" t="str">
-        <x:v>f39260f4b7ce3f28bef5b2b29c23c7c2665d02c37487296fb3f48458ba1b54b4</x:v>
-      </x:c>
-      <x:c r="N5" s="16" t="str">
-        <x:v>53a6060201822c1748a08412275ff581c74b6bf91e892631eda658b31399a2a2</x:v>
-      </x:c>
-      <x:c r="O5" s="16" t="str">
-        <x:v>seedream-5.0-lite</x:v>
-      </x:c>
-      <x:c r="P5" s="16" t="str">
-        <x:v>grok-imagine-video-1.5-fast</x:v>
-      </x:c>
-      <x:c r="Q5" s="20" t="n">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="R5" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S5" s="16" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="T5" s="16" t="str">
-        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="16" t="str">
-        <x:v>v03-s01</x:v>
-      </x:c>
-      <x:c r="B6" s="16" t="str">
-        <x:v>饮水机案例03</x:v>
-      </x:c>
-      <x:c r="C6" s="16" t="str">
-        <x:v>bd6fe4d687c8</x:v>
-      </x:c>
-      <x:c r="D6" s="16" t="str">
-        <x:v>water dispenser</x:v>
-      </x:c>
-      <x:c r="E6" s="16" t="str">
-        <x:v>wide black-and-silver bottom-loading floor dispenser</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="str">
-        <x:v>clean clinic corridor renovation zone</x:v>
-      </x:c>
-      <x:c r="G6" s="16" t="str">
-        <x:v>fully covered with broad side margins and gathered floor edge</x:v>
-      </x:c>
-      <x:c r="H6" s="16" t="str">
-        <x:v>low-angle wide environmental shot</x:v>
-      </x:c>
-      <x:c r="I6" s="16" t="str">
-        <x:v>gentle upward pedestal move</x:v>
-      </x:c>
-      <x:c r="J6" s="16" t="str">
-        <x:v>worker standing at frame right presenting the protected appliance</x:v>
-      </x:c>
-      <x:c r="K6" s="16" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="L6" s="16" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="M6" s="16" t="str">
-        <x:v>77797f056a034f2138e9d0464cc38c4f819d7f8f085291535f66d1fbf0d2b1e4</x:v>
-      </x:c>
-      <x:c r="N6" s="16" t="str">
-        <x:v>0f2381b762c8a7018817fe4d7de4378b081a6f106177bbcbfa1dfa46f7b51262</x:v>
-      </x:c>
-      <x:c r="O6" s="16" t="str">
-        <x:v>seedream-5.0-lite</x:v>
-      </x:c>
-      <x:c r="P6" s="16" t="str">
-        <x:v>grok-imagine-video-1.5-fast</x:v>
-      </x:c>
-      <x:c r="Q6" s="20" t="n">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="R6" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S6" s="16" t="str">
-        <x:v>completed</x:v>
-      </x:c>
-      <x:c r="T6" s="16" t="str">
-        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:T1"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="K4:L6">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="淘汰"/>
-    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="待"/>
-  </x:conditionalFormatting>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5140f1489ca84bfd"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="58" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="58" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="70" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>饮水机提示词档案｜一条提示词对应一条视频</x:v>
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>饮水机提示词档案｜一条提示词对应一条视频</x:v>
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>饮水机提示词档案｜一条提示词对应一条视频</x:v>
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>饮水机提示词档案｜一条提示词对应一条视频</x:v>
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>饮水机提示词档案｜一条提示词对应一条视频</x:v>
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>饮水机提示词档案｜一条提示词对应一条视频</x:v>
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>饮水机提示词档案｜一条提示词对应一条视频</x:v>
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="str">
+        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1001,100 +1125,112 @@
         <x:v>案例ID</x:v>
       </x:c>
       <x:c r="B3" s="15" t="str">
+        <x:v>完整文生视频提示词</x:v>
+      </x:c>
+      <x:c r="C3" s="15" t="str">
+        <x:v>图生视频提示词</x:v>
+      </x:c>
+      <x:c r="D3" s="15" t="str">
         <x:v>首帧提示词</x:v>
       </x:c>
-      <x:c r="C3" s="15" t="str">
-        <x:v>视频提示词</x:v>
-      </x:c>
-      <x:c r="D3" s="15" t="str">
+      <x:c r="E3" s="15" t="str">
         <x:v>负面提示词</x:v>
       </x:c>
-      <x:c r="E3" s="15" t="str">
+      <x:c r="F3" s="15" t="str">
         <x:v>参考图片</x:v>
       </x:c>
-      <x:c r="F3" s="15" t="str">
-        <x:v>首帧提示词哈希</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="str">
-        <x:v>视频提示词哈希</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="132" customHeight="1">
+      <x:c r="G3" s="15" t="str">
+        <x:v>文生视频提示词哈希</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="str">
+        <x:v>图生视频提示词哈希</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="300" customHeight="1">
       <x:c r="A4" s="16" t="str">
         <x:v>v01-s01</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark.</x:v>
+        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: tall narrow floor-standing white dispenser. Environment: cool modern office break room. Coverage state: fully covered to the floor by a straight clear curtain. Shot scale: symmetrical full-body shot. Camera motion: slow right-to-left lateral slider. Person or work state: no person; completed protection state. Opening visual and product geometry: Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
         <x:v>Preserve the cool office break room, tall narrow dispenser and approved intact tape-film geometry. Use a slow right-to-left lateral slider with mild background parallax. The single transparent curtain remains fully connected to the yellow tape and covers the complete dispenser down to the floor. Only fine surface shimmer is allowed. No person enters; no water flow, tear, split, extra tape, duplicate layer, exposed dispenser, installation, transformation, text or logo.</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
+        <x:v>Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
         <x:v>broken plastic, tape wider than film, second tape, uncovered dispenser, water flow</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="str">
+      <x:c r="F4" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="str">
-        <x:v>74d48bd9a5fe57eb</x:v>
-      </x:c>
       <x:c r="G4" s="16" t="str">
+        <x:v>0dd1729bd3ffc618</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
         <x:v>d8d6757fea280462</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="132" customHeight="1">
+    <x:row r="5" ht="300" customHeight="1">
       <x:c r="A5" s="16" t="str">
         <x:v>v02-s01</x:v>
       </x:c>
       <x:c r="B5" s="16" t="str">
-        <x:v>Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark.</x:v>
+        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: compact countertop dispenser. Environment: small renovated apartment kitchen. Coverage state: fully covered from wall tape to below the countertop front edge. Shot scale: three-quarter medium-close shot. Camera motion: slow forward push-in. Person or work state: painter standing at frame left inspecting the tape line without contact. Opening visual and product geometry: Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
         <x:v>Keep the renovated apartment kitchen, compact countertop dispenser, painter and approved continuous tape-film structure unchanged. Perform a slow forward push-in toward the protected appliance. The painter briefly looks from the yellow tape line to the covered counter and remains still without contact. The single clear sheet stays connected endpoint-to-endpoint and continues below the counter edge; the entire dispenser remains behind it. No rip, second layer, extra tape, hand contact, water flow, exposed surface, speech, text or logo.</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
+        <x:v>Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
         <x:v>floor-standing appliance, torn film, hands touching tape, duplicate tape, uncovered counter</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
+      <x:c r="F5" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>338fa81264ef815f</x:v>
-      </x:c>
       <x:c r="G5" s="16" t="str">
+        <x:v>66c7b936edb6b438</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="str">
         <x:v>6bf77b8c6030df84</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="132" customHeight="1">
+    <x:row r="6" ht="300" customHeight="1">
       <x:c r="A6" s="16" t="str">
         <x:v>v03-s01</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
-        <x:v>Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark.</x:v>
+        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: wide black-and-silver bottom-loading floor dispenser. Environment: clean clinic corridor renovation zone. Coverage state: fully covered with broad side margins and gathered floor edge. Shot scale: low-angle wide environmental shot. Camera motion: gentle upward pedestal move. Person or work state: worker standing at frame right presenting the protected appliance. Opening visual and product geometry: Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
       </x:c>
       <x:c r="C6" s="16" t="str">
         <x:v>Preserve the clinic corridor, wide bottom-loading dispenser, standing worker and exact one-piece tape-film installation. Use a gentle upward pedestal move from the gathered floor edge to the yellow tape line. The worker makes one small open-palm presentation gesture beside the covered appliance. The broad transparent sheet remains a single continuous layer with full side margins and stable endpoint alignment. No tear, second flap, loose tape, water flow, contact, uncovered cabinet, camera orbit, speech, text or logo.</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
+        <x:v>Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark.</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
         <x:v>narrow dispenser, ripped film, extra tape, presenter occlusion, open cabinet, water stream</x:v>
       </x:c>
-      <x:c r="E6" s="16" t="str">
+      <x:c r="F6" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
-      <x:c r="F6" s="16" t="str">
-        <x:v>a819165d66578936</x:v>
-      </x:c>
       <x:c r="G6" s="16" t="str">
+        <x:v>591522cb439878e4</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
         <x:v>f5c62dc3f4529607</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7613523b93d44a89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d54d6229a0499d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1185,7 +1321,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc36283069d9647c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbcb48646f454935"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
+++ b/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="Rb7c224934772443a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="R2d1a885bdace42b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="Rd3a51857692b4d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="R48dd4f2dade8426f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="R536826155b994b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="R1ae9cc22ea1a4148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="R3f7e7f16e5964569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="R2c747c48cf734e98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -640,40 +640,40 @@
         <x:v>饮水机案例01</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>water dispenser</x:v>
+        <x:v>饮水机</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>tall narrow floor-standing white dispenser</x:v>
+        <x:v>高窄型白色立式饮水机</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>cool modern office break room</x:v>
+        <x:v>冷色调现代办公室茶水间</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
-        <x:v>fully covered to the floor by a straight clear curtain</x:v>
+        <x:v>一整张笔直透明膜从墙面胶带垂至地面，完整包覆饮水机</x:v>
       </x:c>
       <x:c r="G4" s="16" t="str">
-        <x:v>symmetrical full-body shot</x:v>
+        <x:v>正面对称全身景</x:v>
       </x:c>
       <x:c r="H4" s="16" t="str">
-        <x:v>slow right-to-left lateral slider</x:v>
+        <x:v>镜头从右向左缓慢横移</x:v>
       </x:c>
       <x:c r="I4" s="16" t="str">
-        <x:v>no person; completed protection state</x:v>
+        <x:v>无人物，防护施工已经完成</x:v>
       </x:c>
       <x:c r="J4" s="16" t="str">
-        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: tall narrow floor-standing white dispenser. Environment: cool modern office break room. Coverage state: fully covered to the floor by a straight clear curtain. Shot scale: symmetrical full-body shot. Camera motion: slow right-to-left lateral slider. Person or work state: no person; completed protection state. Opening visual and product geometry: Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：高窄型白色立式饮水机。 环境场景：冷色调现代办公室茶水间。覆盖状态：一整张笔直透明膜从墙面胶带垂至地面，完整包覆饮水机。 镜头景别：正面对称全身景；镜头运动：镜头从右向左缓慢横移。 人物或施工状态：无人物，防护施工已经完成。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。 动态过程：以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
       </x:c>
       <x:c r="K4" s="16" t="str">
-        <x:v>Preserve the cool office break room, tall narrow dispenser and approved intact tape-film geometry. Use a slow right-to-left lateral slider with mild background parallax. The single transparent curtain remains fully connected to the yellow tape and covers the complete dispenser down to the floor. Only fine surface shimmer is allowed. No person enters; no water flow, tear, split, extra tape, duplicate layer, exposed dispenser, installation, transformation, text or logo.</x:v>
+        <x:v>以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。</x:v>
       </x:c>
       <x:c r="L4" s="16" t="str">
-        <x:v>Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark.</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="M4" s="16" t="str">
-        <x:v>broken plastic, tape wider than film, second tape, uncovered dispenser, water flow</x:v>
+        <x:v>破损薄膜、胶带宽于薄膜、第二条胶带、饮水机裸露、出水、人物、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="N4" s="16" t="str">
-        <x:v>0a02369494b1</x:v>
+        <x:v>7d75d337291e</x:v>
       </x:c>
       <x:c r="O4" s="16" t="str">
         <x:v>通过</x:v>
@@ -700,7 +700,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="W4" s="16" t="str">
-        <x:v>completed</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="X4" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
@@ -709,10 +709,10 @@
         <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
       </x:c>
       <x:c r="Z4" s="16" t="str">
-        <x:v>0dd1729bd3ffc618</x:v>
+        <x:v>e629778f3233544e</x:v>
       </x:c>
       <x:c r="AA4" s="16" t="str">
-        <x:v>d8d6757fea280462</x:v>
+        <x:v>311592e0a380bb9d</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="300" customHeight="1">
@@ -723,40 +723,40 @@
         <x:v>饮水机案例02</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>water dispenser</x:v>
+        <x:v>饮水机</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
-        <x:v>compact countertop dispenser</x:v>
+        <x:v>紧凑型台面饮水机</x:v>
       </x:c>
       <x:c r="E5" s="16" t="str">
-        <x:v>small renovated apartment kitchen</x:v>
+        <x:v>正在翻新的小户型公寓厨房</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>fully covered from wall tape to below the countertop front edge</x:v>
+        <x:v>透明膜从墙面胶带连续覆盖饮水机和台面，并延伸至橱柜前沿下方</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str">
-        <x:v>three-quarter medium-close shot</x:v>
+        <x:v>四分之三中近景</x:v>
       </x:c>
       <x:c r="H5" s="16" t="str">
-        <x:v>slow forward push-in</x:v>
+        <x:v>镜头缓慢向前推进</x:v>
       </x:c>
       <x:c r="I5" s="16" t="str">
-        <x:v>painter standing at frame left inspecting the tape line without contact</x:v>
+        <x:v>专业欧美油漆工站在画面左侧，只检查胶带线且不接触产品</x:v>
       </x:c>
       <x:c r="J5" s="16" t="str">
-        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: compact countertop dispenser. Environment: small renovated apartment kitchen. Coverage state: fully covered from wall tape to below the countertop front edge. Shot scale: three-quarter medium-close shot. Camera motion: slow forward push-in. Person or work state: painter standing at frame left inspecting the tape line without contact. Opening visual and product geometry: Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：紧凑型台面饮水机。 环境场景：正在翻新的小户型公寓厨房。覆盖状态：透明膜从墙面胶带连续覆盖饮水机和台面，并延伸至橱柜前沿下方。 镜头景别：四分之三中近景；镜头运动：镜头缓慢向前推进。 人物或施工状态：专业欧美油漆工站在画面左侧，只检查胶带线且不接触产品。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。 动态过程：以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
       </x:c>
       <x:c r="K5" s="16" t="str">
-        <x:v>Keep the renovated apartment kitchen, compact countertop dispenser, painter and approved continuous tape-film structure unchanged. Perform a slow forward push-in toward the protected appliance. The painter briefly looks from the yellow tape line to the covered counter and remains still without contact. The single clear sheet stays connected endpoint-to-endpoint and continues below the counter edge; the entire dispenser remains behind it. No rip, second layer, extra tape, hand contact, water flow, exposed surface, speech, text or logo.</x:v>
+        <x:v>以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="L5" s="16" t="str">
-        <x:v>Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark.</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="M5" s="16" t="str">
-        <x:v>floor-standing appliance, torn film, hands touching tape, duplicate tape, uncovered counter</x:v>
+        <x:v>立式饮水机、破膜、手触碰胶带、重复胶带、台面裸露、额外黄色碎片、出水、文字、标识、水印</x:v>
       </x:c>
       <x:c r="N5" s="16" t="str">
-        <x:v>c2a061a328a2</x:v>
+        <x:v>5958298e633c</x:v>
       </x:c>
       <x:c r="O5" s="16" t="str">
         <x:v>通过</x:v>
@@ -783,7 +783,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="W5" s="16" t="str">
-        <x:v>completed</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="X5" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
@@ -792,10 +792,10 @@
         <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
       </x:c>
       <x:c r="Z5" s="16" t="str">
-        <x:v>66c7b936edb6b438</x:v>
+        <x:v>64444310195d75d5</x:v>
       </x:c>
       <x:c r="AA5" s="16" t="str">
-        <x:v>6bf77b8c6030df84</x:v>
+        <x:v>70a413dec4c3a849</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="300" customHeight="1">
@@ -806,40 +806,40 @@
         <x:v>饮水机案例03</x:v>
       </x:c>
       <x:c r="C6" s="16" t="str">
-        <x:v>water dispenser</x:v>
+        <x:v>饮水机</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
-        <x:v>wide black-and-silver bottom-loading floor dispenser</x:v>
+        <x:v>宽体黑银色下置水桶立式饮水机</x:v>
       </x:c>
       <x:c r="E6" s="16" t="str">
-        <x:v>clean clinic corridor renovation zone</x:v>
+        <x:v>整洁的诊所走廊翻新区</x:v>
       </x:c>
       <x:c r="F6" s="16" t="str">
-        <x:v>fully covered with broad side margins and gathered floor edge</x:v>
+        <x:v>宽幅透明膜完整覆盖饮水机，左右留出宽边，下沿在地面轻微聚拢</x:v>
       </x:c>
       <x:c r="G6" s="16" t="str">
-        <x:v>low-angle wide environmental shot</x:v>
+        <x:v>低机位环境广角镜头</x:v>
       </x:c>
       <x:c r="H6" s="16" t="str">
-        <x:v>gentle upward pedestal move</x:v>
+        <x:v>镜头从地面薄膜下沿缓慢向上抬升至黄色胶带</x:v>
       </x:c>
       <x:c r="I6" s="16" t="str">
-        <x:v>worker standing at frame right presenting the protected appliance</x:v>
+        <x:v>专业欧美油漆工站在画面右侧，在产品旁做展示手势</x:v>
       </x:c>
       <x:c r="J6" s="16" t="str">
-        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: wide black-and-silver bottom-loading floor dispenser. Environment: clean clinic corridor renovation zone. Coverage state: fully covered with broad side margins and gathered floor edge. Shot scale: low-angle wide environmental shot. Camera motion: gentle upward pedestal move. Person or work state: worker standing at frame right presenting the protected appliance. Opening visual and product geometry: Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：宽体黑银色下置水桶立式饮水机。 环境场景：整洁的诊所走廊翻新区。覆盖状态：宽幅透明膜完整覆盖饮水机，左右留出宽边，下沿在地面轻微聚拢。 镜头景别：低机位环境广角镜头；镜头运动：镜头从地面薄膜下沿缓慢向上抬升至黄色胶带。 人物或施工状态：专业欧美油漆工站在画面右侧，在产品旁做展示手势。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。 动态过程：以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
       </x:c>
       <x:c r="K6" s="16" t="str">
-        <x:v>Preserve the clinic corridor, wide bottom-loading dispenser, standing worker and exact one-piece tape-film installation. Use a gentle upward pedestal move from the gathered floor edge to the yellow tape line. The worker makes one small open-palm presentation gesture beside the covered appliance. The broad transparent sheet remains a single continuous layer with full side margins and stable endpoint alignment. No tear, second flap, loose tape, water flow, contact, uncovered cabinet, camera orbit, speech, text or logo.</x:v>
+        <x:v>以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="L6" s="16" t="str">
-        <x:v>Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark.</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="M6" s="16" t="str">
-        <x:v>narrow dispenser, ripped film, extra tape, presenter occlusion, open cabinet, water stream</x:v>
+        <x:v>窄型饮水机、破膜、额外胶带、人物遮挡、下柜打开、出水、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="N6" s="16" t="str">
-        <x:v>bd6fe4d687c8</x:v>
+        <x:v>1b1c6cd8c4ca</x:v>
       </x:c>
       <x:c r="O6" s="16" t="str">
         <x:v>通过</x:v>
@@ -866,7 +866,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="W6" s="16" t="str">
-        <x:v>completed</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="X6" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
@@ -875,10 +875,10 @@
         <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
       </x:c>
       <x:c r="Z6" s="16" t="str">
-        <x:v>591522cb439878e4</x:v>
+        <x:v>e353783f477d89b1</x:v>
       </x:c>
       <x:c r="AA6" s="16" t="str">
-        <x:v>f5c62dc3f4529607</x:v>
+        <x:v>d0e57464d4fdf2aa</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -892,7 +892,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57415b5bfe6b402b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f7ba147ddd749cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1151,25 +1151,25 @@
         <x:v>v01-s01</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: tall narrow floor-standing white dispenser. Environment: cool modern office break room. Coverage state: fully covered to the floor by a straight clear curtain. Shot scale: symmetrical full-body shot. Camera motion: slow right-to-left lateral slider. Person or work state: no person; completed protection state. Opening visual and product geometry: Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：高窄型白色立式饮水机。 环境场景：冷色调现代办公室茶水间。覆盖状态：一整张笔直透明膜从墙面胶带垂至地面，完整包覆饮水机。 镜头景别：正面对称全身景；镜头运动：镜头从右向左缓慢横移。 人物或施工状态：无人物，防护施工已经完成。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。 动态过程：以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>Preserve the cool office break room, tall narrow dispenser and approved intact tape-film geometry. Use a slow right-to-left lateral slider with mild background parallax. The single transparent curtain remains fully connected to the yellow tape and covers the complete dispenser down to the floor. Only fine surface shimmer is allowed. No person enters; no water flow, tear, split, extra tape, duplicate layer, exposed dispenser, installation, transformation, text or logo.</x:v>
+        <x:v>以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>Use the reference only as the exact same-width yellow tape and intact film geometry; create a different appliance shape and office setting. Photorealistic vertical commercial photograph of a tall narrow white floor-standing water dispenser against a cool light-blue painted wall in a modern office break room. Stainless counter edge, stacked paper cups and a covered coffee machine sit far in the background. A single finite yellow masking-tape strip is adhered to the wall 15 centimeters above the dispenser. One straight intact transparent PE sheet begins exactly at both tape endpoints and is permanently bonded across the tape's entire lower edge. It hangs to the floor as one continuous clear curtain in front of and completely around the full dispenser, including control panel, taps, side edges and lower cabinet. No person. Symmetrical full-body framing, cool daylight, generous wall context. No tape overhang, gap, second tape, hole, slit, flap, duplicate sheet, exposed appliance, text, logo or watermark.</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>broken plastic, tape wider than film, second tape, uncovered dispenser, water flow</x:v>
+        <x:v>破损薄膜、胶带宽于薄膜、第二条胶带、饮水机裸露、出水、人物、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="G4" s="16" t="str">
-        <x:v>0dd1729bd3ffc618</x:v>
+        <x:v>e629778f3233544e</x:v>
       </x:c>
       <x:c r="H4" s="16" t="str">
-        <x:v>d8d6757fea280462</x:v>
+        <x:v>311592e0a380bb9d</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="300" customHeight="1">
@@ -1177,25 +1177,25 @@
         <x:v>v02-s01</x:v>
       </x:c>
       <x:c r="B5" s="16" t="str">
-        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: compact countertop dispenser. Environment: small renovated apartment kitchen. Coverage state: fully covered from wall tape to below the countertop front edge. Shot scale: three-quarter medium-close shot. Camera motion: slow forward push-in. Person or work state: painter standing at frame left inspecting the tape line without contact. Opening visual and product geometry: Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：紧凑型台面饮水机。 环境场景：正在翻新的小户型公寓厨房。覆盖状态：透明膜从墙面胶带连续覆盖饮水机和台面，并延伸至橱柜前沿下方。 镜头景别：四分之三中近景；镜头运动：镜头缓慢向前推进。 人物或施工状态：专业欧美油漆工站在画面左侧，只检查胶带线且不接触产品。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。 动态过程：以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>Keep the renovated apartment kitchen, compact countertop dispenser, painter and approved continuous tape-film structure unchanged. Perform a slow forward push-in toward the protected appliance. The painter briefly looks from the yellow tape line to the covered counter and remains still without contact. The single clear sheet stays connected endpoint-to-endpoint and continues below the counter edge; the entire dispenser remains behind it. No rip, second layer, extra tape, hand contact, water flow, exposed surface, speech, text or logo.</x:v>
+        <x:v>以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
-        <x:v>Use the reference only for the strict integrated tape-and-film connection; replace the floor appliance with a visibly compact countertop form and change the environment. Photorealistic vertical commercial photograph of a small white countertop water dispenser on a pale stone counter in an apartment kitchen under repainting. A smooth off-white backsplash wall rises behind it. One finite yellow masking-tape strip is adhered to the backsplash 12 centimeters above the appliance. Exactly one transparent PE film sheet is permanently bonded along the tape's full lower edge, with square left and right endpoints aligned exactly. The intact clear sheet passes in front of the complete countertop dispenser and continues below the counter's front edge, protecting both appliance and immediate work surface as one continuous layer. A professional European painter stands at far frame left, looking at the tape line without touching or blocking it. Three-quarter medium-close view, warm daylight, visible cabinet and paint tray context. No tear, opening, doubled film, extra tape, tape overhang, exposed appliance, text, logo or watermark.</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="E5" s="16" t="str">
-        <x:v>floor-standing appliance, torn film, hands touching tape, duplicate tape, uncovered counter</x:v>
+        <x:v>立式饮水机、破膜、手触碰胶带、重复胶带、台面裸露、额外黄色碎片、出水、文字、标识、水印</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str">
-        <x:v>66c7b936edb6b438</x:v>
+        <x:v>64444310195d75d5</x:v>
       </x:c>
       <x:c r="H5" s="16" t="str">
-        <x:v>6bf77b8c6030df84</x:v>
+        <x:v>70a413dec4c3a849</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="300" customHeight="1">
@@ -1203,25 +1203,25 @@
         <x:v>v03-s01</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
-        <x:v>Create a 10-second vertical 9:16 photorealistic renovation product demonstration video. Object: water dispenser; form: wide black-and-silver bottom-loading floor dispenser. Environment: clean clinic corridor renovation zone. Coverage state: fully covered with broad side margins and gathered floor edge. Shot scale: low-angle wide environmental shot. Camera motion: gentle upward pedestal move. Person or work state: worker standing at frame right presenting the protected appliance. Opening visual and product geometry: Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark. Throughout the entire shot, the transparent PE film must remain one continuous intact sheet permanently bonded along the full lower edge of one straight yellow masking-tape strip. Keep the target object fully behind the film with no holes, tears, splits, duplicated film, extra tape, exposed object, text, logo or watermark.</x:v>
+        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：宽体黑银色下置水桶立式饮水机。 环境场景：整洁的诊所走廊翻新区。覆盖状态：宽幅透明膜完整覆盖饮水机，左右留出宽边，下沿在地面轻微聚拢。 镜头景别：低机位环境广角镜头；镜头运动：镜头从地面薄膜下沿缓慢向上抬升至黄色胶带。 人物或施工状态：专业欧美油漆工站在画面右侧，在产品旁做展示手势。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。 动态过程：以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
       </x:c>
       <x:c r="C6" s="16" t="str">
-        <x:v>Preserve the clinic corridor, wide bottom-loading dispenser, standing worker and exact one-piece tape-film installation. Use a gentle upward pedestal move from the gathered floor edge to the yellow tape line. The worker makes one small open-palm presentation gesture beside the covered appliance. The broad transparent sheet remains a single continuous layer with full side margins and stable endpoint alignment. No tear, second flap, loose tape, water flow, contact, uncovered cabinet, camera orbit, speech, text or logo.</x:v>
+        <x:v>以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
-        <x:v>Use the reference only as the exact geometry rule for one finite yellow tape strip bonded to one intact film sheet; create a wide appliance and clearly different clinic environment. Photorealistic vertical commercial photograph of a wide black-and-silver bottom-loading floor water dispenser in a clean clinic corridor renovation zone, against a smooth white wall with a covered rolling cart and blue door softly visible in the distance. One finite yellow masking-tape strip is fixed to the wall 18 centimeters above the dispenser. One broad transparent PE film sheet has exactly the same width and is continuously bonded to the entire tape lower edge. It falls as one unbroken layer over the full top, control panel, taps, wide side edges and bottom-loading cabinet, ending in a lightly gathered but continuous floor edge. A professional worker in white painter clothing stands at far frame right and presents beside the appliance with an open palm without touching or blocking it. Low-angle wide environmental composition. No split, seam, opening, double flap, additional tape, tape overhang, exposed cabinet, text, logo or watermark.</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="E6" s="16" t="str">
-        <x:v>narrow dispenser, ripped film, extra tape, presenter occlusion, open cabinet, water stream</x:v>
+        <x:v>窄型饮水机、破膜、额外胶带、人物遮挡、下柜打开、出水、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="F6" s="16" t="str">
         <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="G6" s="16" t="str">
-        <x:v>591522cb439878e4</x:v>
+        <x:v>e353783f477d89b1</x:v>
       </x:c>
       <x:c r="H6" s="16" t="str">
-        <x:v>f5c62dc3f4529607</x:v>
+        <x:v>d0e57464d4fdf2aa</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1230,7 +1230,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47d54d6229a0499d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfce3c82e3ab94a11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1321,7 +1321,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbcb48646f454935"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab9d80f0c7654348"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
+++ b/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="R536826155b994b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="R1ae9cc22ea1a4148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="R3f7e7f16e5964569"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="R2c747c48cf734e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="Rb08c4362b6a44b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="Rb79599d6dd5e43bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="Rb6b46674e3144cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="Ra0237d82ae3d4257"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,8 +180,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DispenserVideoStrategy" displayName="DispenserVideoStrategy" ref="A3:AA6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="27">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DispenserVideoStrategy" displayName="DispenserVideoStrategy" ref="A3:Y6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="25">
     <x:tableColumn id="1" name="案例ID"/>
     <x:tableColumn id="2" name="案例名称"/>
     <x:tableColumn id="3" name="物体种类"/>
@@ -191,40 +191,36 @@
     <x:tableColumn id="7" name="镜头景别"/>
     <x:tableColumn id="8" name="镜头运动"/>
     <x:tableColumn id="9" name="人物/施工状态"/>
-    <x:tableColumn id="10" name="完整文生视频提示词"/>
-    <x:tableColumn id="11" name="图生视频提示词"/>
-    <x:tableColumn id="12" name="首帧提示词"/>
-    <x:tableColumn id="13" name="负面提示词"/>
-    <x:tableColumn id="14" name="唯一组合指纹"/>
-    <x:tableColumn id="15" name="首帧状态"/>
-    <x:tableColumn id="16" name="视频状态"/>
-    <x:tableColumn id="17" name="图片哈希"/>
-    <x:tableColumn id="18" name="视频哈希"/>
-    <x:tableColumn id="19" name="图片模型"/>
-    <x:tableColumn id="20" name="视频模型"/>
-    <x:tableColumn id="21" name="预计视频费用（元）"/>
-    <x:tableColumn id="22" name="生成秒数"/>
-    <x:tableColumn id="23" name="任务状态"/>
-    <x:tableColumn id="24" name="参考图片"/>
-    <x:tableColumn id="25" name="项目相对路径"/>
-    <x:tableColumn id="26" name="文生视频提示词哈希"/>
-    <x:tableColumn id="27" name="图生视频提示词哈希"/>
+    <x:tableColumn id="10" name="视频生成提示词（图生视频）"/>
+    <x:tableColumn id="11" name="首帧提示词（文生图）"/>
+    <x:tableColumn id="12" name="负面提示词"/>
+    <x:tableColumn id="13" name="唯一组合指纹"/>
+    <x:tableColumn id="14" name="首帧状态"/>
+    <x:tableColumn id="15" name="视频状态"/>
+    <x:tableColumn id="16" name="图片哈希"/>
+    <x:tableColumn id="17" name="视频哈希"/>
+    <x:tableColumn id="18" name="图片模型"/>
+    <x:tableColumn id="19" name="视频模型"/>
+    <x:tableColumn id="20" name="预计视频费用（元）"/>
+    <x:tableColumn id="21" name="生成秒数"/>
+    <x:tableColumn id="22" name="任务状态"/>
+    <x:tableColumn id="23" name="参考图片"/>
+    <x:tableColumn id="24" name="项目相对路径"/>
+    <x:tableColumn id="25" name="视频提示词哈希"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DispenserPromptArchive" displayName="DispenserPromptArchive" ref="A3:H6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DispenserPromptArchive" displayName="DispenserPromptArchive" ref="A3:F6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
     <x:tableColumn id="1" name="案例ID"/>
-    <x:tableColumn id="2" name="完整文生视频提示词"/>
-    <x:tableColumn id="3" name="图生视频提示词"/>
-    <x:tableColumn id="4" name="首帧提示词"/>
-    <x:tableColumn id="5" name="负面提示词"/>
-    <x:tableColumn id="6" name="参考图片"/>
-    <x:tableColumn id="7" name="文生视频提示词哈希"/>
-    <x:tableColumn id="8" name="图生视频提示词哈希"/>
+    <x:tableColumn id="2" name="视频生成提示词（图生视频）"/>
+    <x:tableColumn id="3" name="首帧提示词（文生图）"/>
+    <x:tableColumn id="4" name="负面提示词"/>
+    <x:tableColumn id="5" name="参考图片"/>
+    <x:tableColumn id="6" name="视频提示词哈希"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -449,104 +445,96 @@
     <x:col min="10" max="10" width="70" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="70" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="70" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="70" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="16" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="16" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="34" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="38" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="16" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="16" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="34" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="38" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="K1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="L1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="M1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="N1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="O1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="P1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="Q1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="R1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="S1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="T1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="U1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="V1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="W1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="X1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
       <x:c r="Y1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
-      </x:c>
-      <x:c r="Z1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
-      </x:c>
-      <x:c r="AA1" s="3" t="str">
-        <x:v>饮水机视频策略库｜七个维度 + 一条组合对应一条文生视频提示词</x:v>
+        <x:v>饮水机视频策略库｜七个维度 + 首帧提示词 + 实际视频生成提示词</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -578,58 +566,52 @@
         <x:v>人物/施工状态</x:v>
       </x:c>
       <x:c r="J3" s="15" t="str">
-        <x:v>完整文生视频提示词</x:v>
+        <x:v>视频生成提示词（图生视频）</x:v>
       </x:c>
       <x:c r="K3" s="15" t="str">
-        <x:v>图生视频提示词</x:v>
+        <x:v>首帧提示词（文生图）</x:v>
       </x:c>
       <x:c r="L3" s="15" t="str">
-        <x:v>首帧提示词</x:v>
+        <x:v>负面提示词</x:v>
       </x:c>
       <x:c r="M3" s="15" t="str">
-        <x:v>负面提示词</x:v>
+        <x:v>唯一组合指纹</x:v>
       </x:c>
       <x:c r="N3" s="15" t="str">
-        <x:v>唯一组合指纹</x:v>
+        <x:v>首帧状态</x:v>
       </x:c>
       <x:c r="O3" s="15" t="str">
-        <x:v>首帧状态</x:v>
+        <x:v>视频状态</x:v>
       </x:c>
       <x:c r="P3" s="15" t="str">
-        <x:v>视频状态</x:v>
+        <x:v>图片哈希</x:v>
       </x:c>
       <x:c r="Q3" s="15" t="str">
-        <x:v>图片哈希</x:v>
+        <x:v>视频哈希</x:v>
       </x:c>
       <x:c r="R3" s="15" t="str">
-        <x:v>视频哈希</x:v>
+        <x:v>图片模型</x:v>
       </x:c>
       <x:c r="S3" s="15" t="str">
-        <x:v>图片模型</x:v>
+        <x:v>视频模型</x:v>
       </x:c>
       <x:c r="T3" s="15" t="str">
-        <x:v>视频模型</x:v>
+        <x:v>预计视频费用（元）</x:v>
       </x:c>
       <x:c r="U3" s="15" t="str">
-        <x:v>预计视频费用（元）</x:v>
+        <x:v>生成秒数</x:v>
       </x:c>
       <x:c r="V3" s="15" t="str">
-        <x:v>生成秒数</x:v>
+        <x:v>任务状态</x:v>
       </x:c>
       <x:c r="W3" s="15" t="str">
-        <x:v>任务状态</x:v>
+        <x:v>参考图片</x:v>
       </x:c>
       <x:c r="X3" s="15" t="str">
-        <x:v>参考图片</x:v>
-      </x:c>
-      <x:c r="Y3" s="15" t="str">
         <x:v>项目相对路径</x:v>
       </x:c>
-      <x:c r="Z3" s="15" t="str">
-        <x:v>文生视频提示词哈希</x:v>
-      </x:c>
-      <x:c r="AA3" s="11" t="str">
-        <x:v>图生视频提示词哈希</x:v>
+      <x:c r="Y3" s="11" t="str">
+        <x:v>视频提示词哈希</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="300" customHeight="1">
@@ -661,57 +643,51 @@
         <x:v>无人物，防护施工已经完成</x:v>
       </x:c>
       <x:c r="J4" s="16" t="str">
-        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：高窄型白色立式饮水机。 环境场景：冷色调现代办公室茶水间。覆盖状态：一整张笔直透明膜从墙面胶带垂至地面，完整包覆饮水机。 镜头景别：正面对称全身景；镜头运动：镜头从右向左缓慢横移。 人物或施工状态：无人物，防护施工已经完成。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。 动态过程：以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
+        <x:v>以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。</x:v>
       </x:c>
       <x:c r="K4" s="16" t="str">
-        <x:v>以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="L4" s="16" t="str">
-        <x:v>生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。</x:v>
+        <x:v>破损薄膜、胶带宽于薄膜、第二条胶带、饮水机裸露、出水、人物、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="M4" s="16" t="str">
-        <x:v>破损薄膜、胶带宽于薄膜、第二条胶带、饮水机裸露、出水、人物、双层膜、文字、标识、水印</x:v>
+        <x:v>7d75d337291e</x:v>
       </x:c>
       <x:c r="N4" s="16" t="str">
-        <x:v>7d75d337291e</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="O4" s="16" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="P4" s="16" t="str">
-        <x:v>通过</x:v>
+        <x:v>13e513264b9feae344fecb4235e667fcb411f01f54ecf1351d125ff44088771a</x:v>
       </x:c>
       <x:c r="Q4" s="16" t="str">
-        <x:v>13e513264b9feae344fecb4235e667fcb411f01f54ecf1351d125ff44088771a</x:v>
+        <x:v>3e301610ebab3909b68f7fe3e911362108008c94e1075cbef0bc5533860ae005</x:v>
       </x:c>
       <x:c r="R4" s="16" t="str">
-        <x:v>3e301610ebab3909b68f7fe3e911362108008c94e1075cbef0bc5533860ae005</x:v>
+        <x:v>seedream-5.0-lite</x:v>
       </x:c>
       <x:c r="S4" s="16" t="str">
-        <x:v>seedream-5.0-lite</x:v>
-      </x:c>
-      <x:c r="T4" s="16" t="str">
         <x:v>grok-imagine-video-1.5-fast</x:v>
       </x:c>
-      <x:c r="U4" s="20" t="n">
+      <x:c r="T4" s="20" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="V4" s="16" t="n">
+      <x:c r="U4" s="16" t="n">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="V4" s="16" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
       <x:c r="W4" s="16" t="str">
-        <x:v>已完成</x:v>
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="X4" s="16" t="str">
-        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
+        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
       </x:c>
       <x:c r="Y4" s="16" t="str">
-        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
-      </x:c>
-      <x:c r="Z4" s="16" t="str">
-        <x:v>e629778f3233544e</x:v>
-      </x:c>
-      <x:c r="AA4" s="16" t="str">
         <x:v>311592e0a380bb9d</x:v>
       </x:c>
     </x:row>
@@ -744,57 +720,51 @@
         <x:v>专业欧美油漆工站在画面左侧，只检查胶带线且不接触产品</x:v>
       </x:c>
       <x:c r="J5" s="16" t="str">
-        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：紧凑型台面饮水机。 环境场景：正在翻新的小户型公寓厨房。覆盖状态：透明膜从墙面胶带连续覆盖饮水机和台面，并延伸至橱柜前沿下方。 镜头景别：四分之三中近景；镜头运动：镜头缓慢向前推进。 人物或施工状态：专业欧美油漆工站在画面左侧，只检查胶带线且不接触产品。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。 动态过程：以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
+        <x:v>以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="K5" s="16" t="str">
-        <x:v>以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="L5" s="16" t="str">
-        <x:v>生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。</x:v>
+        <x:v>立式饮水机、破膜、手触碰胶带、重复胶带、台面裸露、额外黄色碎片、出水、文字、标识、水印</x:v>
       </x:c>
       <x:c r="M5" s="16" t="str">
-        <x:v>立式饮水机、破膜、手触碰胶带、重复胶带、台面裸露、额外黄色碎片、出水、文字、标识、水印</x:v>
+        <x:v>5958298e633c</x:v>
       </x:c>
       <x:c r="N5" s="16" t="str">
-        <x:v>5958298e633c</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="O5" s="16" t="str">
-        <x:v>通过</x:v>
+        <x:v>淘汰</x:v>
       </x:c>
       <x:c r="P5" s="16" t="str">
-        <x:v>淘汰</x:v>
+        <x:v>f39260f4b7ce3f28bef5b2b29c23c7c2665d02c37487296fb3f48458ba1b54b4</x:v>
       </x:c>
       <x:c r="Q5" s="16" t="str">
-        <x:v>f39260f4b7ce3f28bef5b2b29c23c7c2665d02c37487296fb3f48458ba1b54b4</x:v>
+        <x:v>53a6060201822c1748a08412275ff581c74b6bf91e892631eda658b31399a2a2</x:v>
       </x:c>
       <x:c r="R5" s="16" t="str">
-        <x:v>53a6060201822c1748a08412275ff581c74b6bf91e892631eda658b31399a2a2</x:v>
+        <x:v>seedream-5.0-lite</x:v>
       </x:c>
       <x:c r="S5" s="16" t="str">
-        <x:v>seedream-5.0-lite</x:v>
-      </x:c>
-      <x:c r="T5" s="16" t="str">
         <x:v>grok-imagine-video-1.5-fast</x:v>
       </x:c>
-      <x:c r="U5" s="20" t="n">
+      <x:c r="T5" s="20" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="V5" s="16" t="n">
+      <x:c r="U5" s="16" t="n">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="V5" s="16" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
       <x:c r="W5" s="16" t="str">
-        <x:v>已完成</x:v>
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="X5" s="16" t="str">
-        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
+        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
       </x:c>
       <x:c r="Y5" s="16" t="str">
-        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
-      </x:c>
-      <x:c r="Z5" s="16" t="str">
-        <x:v>64444310195d75d5</x:v>
-      </x:c>
-      <x:c r="AA5" s="16" t="str">
         <x:v>70a413dec4c3a849</x:v>
       </x:c>
     </x:row>
@@ -827,72 +797,66 @@
         <x:v>专业欧美油漆工站在画面右侧，在产品旁做展示手势</x:v>
       </x:c>
       <x:c r="J6" s="16" t="str">
-        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：宽体黑银色下置水桶立式饮水机。 环境场景：整洁的诊所走廊翻新区。覆盖状态：宽幅透明膜完整覆盖饮水机，左右留出宽边，下沿在地面轻微聚拢。 镜头景别：低机位环境广角镜头；镜头运动：镜头从地面薄膜下沿缓慢向上抬升至黄色胶带。 人物或施工状态：专业欧美油漆工站在画面右侧，在产品旁做展示手势。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。 动态过程：以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
+        <x:v>以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="K6" s="16" t="str">
-        <x:v>以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="L6" s="16" t="str">
-        <x:v>生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。</x:v>
+        <x:v>窄型饮水机、破膜、额外胶带、人物遮挡、下柜打开、出水、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="M6" s="16" t="str">
-        <x:v>窄型饮水机、破膜、额外胶带、人物遮挡、下柜打开、出水、双层膜、文字、标识、水印</x:v>
+        <x:v>1b1c6cd8c4ca</x:v>
       </x:c>
       <x:c r="N6" s="16" t="str">
-        <x:v>1b1c6cd8c4ca</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="O6" s="16" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="P6" s="16" t="str">
-        <x:v>通过</x:v>
+        <x:v>77797f056a034f2138e9d0464cc38c4f819d7f8f085291535f66d1fbf0d2b1e4</x:v>
       </x:c>
       <x:c r="Q6" s="16" t="str">
-        <x:v>77797f056a034f2138e9d0464cc38c4f819d7f8f085291535f66d1fbf0d2b1e4</x:v>
+        <x:v>0f2381b762c8a7018817fe4d7de4378b081a6f106177bbcbfa1dfa46f7b51262</x:v>
       </x:c>
       <x:c r="R6" s="16" t="str">
-        <x:v>0f2381b762c8a7018817fe4d7de4378b081a6f106177bbcbfa1dfa46f7b51262</x:v>
+        <x:v>seedream-5.0-lite</x:v>
       </x:c>
       <x:c r="S6" s="16" t="str">
-        <x:v>seedream-5.0-lite</x:v>
-      </x:c>
-      <x:c r="T6" s="16" t="str">
         <x:v>grok-imagine-video-1.5-fast</x:v>
       </x:c>
-      <x:c r="U6" s="20" t="n">
+      <x:c r="T6" s="20" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="V6" s="16" t="n">
+      <x:c r="U6" s="16" t="n">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="V6" s="16" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
       <x:c r="W6" s="16" t="str">
-        <x:v>已完成</x:v>
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="X6" s="16" t="str">
-        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
+        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
       </x:c>
       <x:c r="Y6" s="16" t="str">
-        <x:v>03_视频项目/防尘膜短视频/08_场景单元/07_饮水机_差异化场景/技术记录（不用看）</x:v>
-      </x:c>
-      <x:c r="Z6" s="16" t="str">
-        <x:v>e353783f477d89b1</x:v>
-      </x:c>
-      <x:c r="AA6" s="16" t="str">
         <x:v>d0e57464d4fdf2aa</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:AA1"/>
+    <x:mergeCell ref="A1:Y1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="O4:P6">
+  <x:conditionalFormatting sqref="N4:O6">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="淘汰"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="待"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f7ba147ddd749cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346c0e11d0774a46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -967,7 +931,7 @@
         <x:v>唯一七维组合数</x:v>
       </x:c>
       <x:c r="B5" s="17" t="n">
-        <x:f>COUNTA('视频策略库'!$N$4:$N$100)</x:f>
+        <x:f>COUNTA('视频策略库'!$M$4:$M$100)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="17"/>
@@ -980,7 +944,7 @@
         <x:v>首帧通过数</x:v>
       </x:c>
       <x:c r="B6" s="17" t="n">
-        <x:f>COUNTIF('视频策略库'!$O$4:$O$100,"通过")</x:f>
+        <x:f>COUNTIF('视频策略库'!$N$4:$N$100,"通过")</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="17"/>
@@ -993,7 +957,7 @@
         <x:v>视频通过数</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
-        <x:f>COUNTIF('视频策略库'!$P$4:$P$100,"通过")</x:f>
+        <x:f>COUNTIF('视频策略库'!$O$4:$O$100,"通过")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="17"/>
@@ -1006,7 +970,7 @@
         <x:v>预计视频费用（元）</x:v>
       </x:c>
       <x:c r="B8" s="18" t="n">
-        <x:f>ROUND(SUM('视频策略库'!$U$4:$U$100),2)</x:f>
+        <x:f>ROUND(SUM('视频策略库'!$T$4:$T$100),2)</x:f>
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="C8" s="17"/>
@@ -1049,7 +1013,7 @@
         <x:v>台账定位</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>主表逐行列出七维组合及其完整文生视频提示词；统计页仅用于辅助查看</x:v>
+        <x:v>主表逐行列出七维组合、首帧提示词和实际使用的视频生成提示词；统计页仅用于辅助查看</x:v>
       </x:c>
       <x:c r="C12" s="19"/>
       <x:c r="D12" s="19"/>
@@ -1087,37 +1051,29 @@
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="70" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
+        <x:v>饮水机提示词档案｜真实流水线：首帧文生图 → 图生视频</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
+        <x:v>饮水机提示词档案｜真实流水线：首帧文生图 → 图生视频</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
+        <x:v>饮水机提示词档案｜真实流水线：首帧文生图 → 图生视频</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
+        <x:v>饮水机提示词档案｜真实流水线：首帧文生图 → 图生视频</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
+        <x:v>饮水机提示词档案｜真实流水线：首帧文生图 → 图生视频</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>饮水机提示词档案｜区分文生视频、图生视频与首帧提示词</x:v>
+        <x:v>饮水机提示词档案｜真实流水线：首帧文生图 → 图生视频</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1125,25 +1081,19 @@
         <x:v>案例ID</x:v>
       </x:c>
       <x:c r="B3" s="15" t="str">
-        <x:v>完整文生视频提示词</x:v>
+        <x:v>视频生成提示词（图生视频）</x:v>
       </x:c>
       <x:c r="C3" s="15" t="str">
-        <x:v>图生视频提示词</x:v>
+        <x:v>首帧提示词（文生图）</x:v>
       </x:c>
       <x:c r="D3" s="15" t="str">
-        <x:v>首帧提示词</x:v>
+        <x:v>负面提示词</x:v>
       </x:c>
       <x:c r="E3" s="15" t="str">
-        <x:v>负面提示词</x:v>
-      </x:c>
-      <x:c r="F3" s="15" t="str">
         <x:v>参考图片</x:v>
       </x:c>
-      <x:c r="G3" s="15" t="str">
-        <x:v>文生视频提示词哈希</x:v>
-      </x:c>
-      <x:c r="H3" s="11" t="str">
-        <x:v>图生视频提示词哈希</x:v>
+      <x:c r="F3" s="11" t="str">
+        <x:v>视频提示词哈希</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="300" customHeight="1">
@@ -1151,24 +1101,18 @@
         <x:v>v01-s01</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：高窄型白色立式饮水机。 环境场景：冷色调现代办公室茶水间。覆盖状态：一整张笔直透明膜从墙面胶带垂至地面，完整包覆饮水机。 镜头景别：正面对称全身景；镜头运动：镜头从右向左缓慢横移。 人物或施工状态：无人物，防护施工已经完成。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。 动态过程：以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
+        <x:v>以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>以已批准的办公室茶水间首帧为起点，保持高窄型饮水机以及胶带与透明膜的一体式结构不变。镜头从右向左缓慢横移，背景产生轻微视差；整张透明膜始终连接黄色胶带并垂至地面，完整覆盖饮水机，只允许细微表面反光。禁止人物进入、禁止出水、禁止撕裂、禁止第二层膜、禁止新增胶带、禁止饮水机裸露、禁止文字和标识。</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>生成一张9:16竖屏写实商业摄影首帧：冷色调现代办公室茶水间内，一台高窄型白色立式饮水机靠浅蓝色墙面摆放。饮水机上方约15厘米的墙面粘贴一条长度有限、笔直完整的黄色美纹胶带；一整张与胶带同宽的透明PE膜永久连接在胶带下沿，从左右端点笔直垂至地面，完整覆盖饮水机顶部、控制面板、出水口、侧边和下柜。无人物，正面对称全身构图，冷色自然日光，背景仅保留不抢眼的纸杯和操作台，无第二条胶带、无破口、无饮水机裸露、无文字、标识或水印。</x:v>
+        <x:v>破损薄膜、胶带宽于薄膜、第二条胶带、饮水机裸露、出水、人物、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>破损薄膜、胶带宽于薄膜、第二条胶带、饮水机裸露、出水、人物、双层膜、文字、标识、水印</x:v>
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
-        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
-      </x:c>
-      <x:c r="G4" s="16" t="str">
-        <x:v>e629778f3233544e</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="str">
         <x:v>311592e0a380bb9d</x:v>
       </x:c>
     </x:row>
@@ -1177,24 +1121,18 @@
         <x:v>v02-s01</x:v>
       </x:c>
       <x:c r="B5" s="16" t="str">
-        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：紧凑型台面饮水机。 环境场景：正在翻新的小户型公寓厨房。覆盖状态：透明膜从墙面胶带连续覆盖饮水机和台面，并延伸至橱柜前沿下方。 镜头景别：四分之三中近景；镜头运动：镜头缓慢向前推进。 人物或施工状态：专业欧美油漆工站在画面左侧，只检查胶带线且不接触产品。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。 动态过程：以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
+        <x:v>以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>以已批准的公寓厨房首帧为起点，保持台面饮水机、油漆工以及连续的一体式胶带薄膜结构不变。镜头缓慢向前推进；油漆工只把视线从黄色胶带移向被覆盖的台面，身体保持静止，不触碰产品。透明膜始终从胶带端点连续延伸至橱柜前沿下方，饮水机和台面全程位于膜后。禁止撕裂、第二层膜、额外胶带、手部接触、出水、裸露表面、说话、文字和标识。</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
-        <x:v>生成一张9:16竖屏写实商业摄影首帧：正在翻新的小户型公寓厨房内，一台紧凑型白色台面饮水机放在浅色石材台面上。饮水机上方约12厘米的墙面粘贴一条有限长度的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带整个下沿，左右端点严格对齐，连续覆盖完整饮水机、周边台面并延伸至橱柜前沿下方。专业欧美男油漆工站在画面最左侧，只观察胶带线，不接触、不遮挡产品。四分之三中近景，暖色日光，可见橱柜和油漆托盘，无撕裂、无额外胶带、无裸露台面、无文字、标识或水印。</x:v>
+        <x:v>立式饮水机、破膜、手触碰胶带、重复胶带、台面裸露、额外黄色碎片、出水、文字、标识、水印</x:v>
       </x:c>
       <x:c r="E5" s="16" t="str">
-        <x:v>立式饮水机、破膜、手触碰胶带、重复胶带、台面裸露、额外黄色碎片、出水、文字、标识、水印</x:v>
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
-        <x:v>64444310195d75d5</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="str">
         <x:v>70a413dec4c3a849</x:v>
       </x:c>
     </x:row>
@@ -1203,34 +1141,28 @@
         <x:v>v03-s01</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
-        <x:v>生成一条10秒、9:16竖屏、写实装修广告风格的视频。 物体种类：饮水机；物体形态：宽体黑银色下置水桶立式饮水机。 环境场景：整洁的诊所走廊翻新区。覆盖状态：宽幅透明膜完整覆盖饮水机，左右留出宽边，下沿在地面轻微聚拢。 镜头景别：低机位环境广角镜头；镜头运动：镜头从地面薄膜下沿缓慢向上抬升至黄色胶带。 人物或施工状态：专业欧美油漆工站在画面右侧，在产品旁做展示手势。 首帧与产品结构：生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。 动态过程：以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。 全程硬性要求：透明PE薄膜必须始终是一整张连续完整的薄膜，并永久连接在同一条笔直黄色美纹胶带的整个下沿；目标物必须始终完整位于薄膜后方。不得出现孔洞、撕裂、分叉、重复薄膜、额外胶带、目标物裸露、文字、标识或水印。</x:v>
+        <x:v>以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。</x:v>
       </x:c>
       <x:c r="C6" s="16" t="str">
-        <x:v>以已批准的诊所走廊首帧为起点，保持宽体饮水机、站立油漆工和一体式胶带薄膜结构不变。镜头从地面轻微聚拢的薄膜下沿缓慢向上抬升至黄色胶带；油漆工只做一次小幅开放手掌展示动作。宽幅透明膜始终是一整张连续材料，左右边界和胶带端点稳定对齐。禁止撕裂、第二片薄膜、松脱胶带、额外胶带、出水、接触产品、下柜裸露、环绕运镜、说话、文字和标识。</x:v>
+        <x:v>生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
-        <x:v>生成一张9:16竖屏写实商业摄影首帧：整洁的诊所走廊翻新区内，一台宽体黑银色下置水桶立式饮水机靠平整白墙摆放。饮水机上方约18厘米的墙面固定一条有限长度、笔直完整的黄色美纹胶带；一整张同宽透明PE膜永久连接在胶带下沿全长，连续覆盖饮水机顶部、控制面板、出水口、宽侧边和下柜，左右留出清晰宽边，下沿在地面轻微聚拢但保持连续。专业欧美油漆工站在画面最右侧，在薄膜边界外做开放手掌展示动作，不接触、不遮挡产品。低机位环境广角，无文字、标识或水印。</x:v>
+        <x:v>窄型饮水机、破膜、额外胶带、人物遮挡、下柜打开、出水、双层膜、文字、标识、水印</x:v>
       </x:c>
       <x:c r="E6" s="16" t="str">
-        <x:v>窄型饮水机、破膜、额外胶带、人物遮挡、下柜打开、出水、双层膜、文字、标识、水印</x:v>
+        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
       </x:c>
       <x:c r="F6" s="16" t="str">
-        <x:v>../../05_饮水机_墙面固定_完整膜返工/技术记录（不用看）/approved-candidates/饮水机完整膜基准.png</x:v>
-      </x:c>
-      <x:c r="G6" s="16" t="str">
-        <x:v>e353783f477d89b1</x:v>
-      </x:c>
-      <x:c r="H6" s="16" t="str">
         <x:v>d0e57464d4fdf2aa</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A1:F1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfce3c82e3ab94a11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd68317dd1a74f16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1321,7 +1253,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab9d80f0c7654348"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69d7c705d23040ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
+++ b/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="Rb08c4362b6a44b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="Rb79599d6dd5e43bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="Rb6b46674e3144cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="Ra0237d82ae3d4257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="R4a8bd0f1742740b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="Rb0278b27a6eb482b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="Rcd05b99362b24e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="Re094b74208eb426b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -856,7 +856,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346c0e11d0774a46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc07c518545a447c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -967,7 +967,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="str">
-        <x:v>预计视频费用（元）</x:v>
+        <x:v>全部案例预计视频费用（元）</x:v>
       </x:c>
       <x:c r="B8" s="18" t="n">
         <x:f>ROUND(SUM('视频策略库'!$T$4:$T$100),2)</x:f>
@@ -998,10 +998,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="19" t="str">
-        <x:v>机器执行源</x:v>
+        <x:v>数据来源</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>技术记录（不用看）/project.json</x:v>
+        <x:v>已生成案例来自 project.json；待生成案例为台账中的策略计划</x:v>
       </x:c>
       <x:c r="C11" s="19"/>
       <x:c r="D11" s="19"/>
@@ -1013,7 +1013,7 @@
         <x:v>台账定位</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>主表逐行列出七维组合、首帧提示词和实际使用的视频生成提示词；统计页仅用于辅助查看</x:v>
+        <x:v>主表逐行列出七维组合、首帧提示词和对应的视频生成提示词；待生成案例不计为已完成</x:v>
       </x:c>
       <x:c r="C12" s="19"/>
       <x:c r="D12" s="19"/>
@@ -1162,7 +1162,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd68317dd1a74f16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R550bd0eb68704f4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1253,7 +1253,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69d7c705d23040ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7852d4fae13847ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
+++ b/03_视频项目/防尘膜短视频/08_场景单元/素材策略台账/2026-07-17-差异化批次/饮水机素材策略台账.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="R4a8bd0f1742740b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="Rb0278b27a6eb482b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="Rcd05b99362b24e08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="Re094b74208eb426b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视频策略库" sheetId="1" r:id="R969bdd090c184207"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="策略总览" sheetId="2" r:id="R8f7b2f5d74e84a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="提示词档案" sheetId="3" r:id="Rf94a9f75edc443cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="淘汰记录" sheetId="4" r:id="Rafaa15be00684ebb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -856,7 +856,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc07c518545a447c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05f039d52ffd4566"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1001,7 +1001,7 @@
         <x:v>数据来源</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>已生成案例来自 project.json；待生成案例为台账中的策略计划</x:v>
+        <x:v>案例策略来自 project.json；生成状态来自首帧、视频哈希验收记录</x:v>
       </x:c>
       <x:c r="C11" s="19"/>
       <x:c r="D11" s="19"/>
@@ -1013,7 +1013,7 @@
         <x:v>台账定位</x:v>
       </x:c>
       <x:c r="B12" s="19" t="str">
-        <x:v>主表逐行列出七维组合、首帧提示词和对应的视频生成提示词；待生成案例不计为已完成</x:v>
+        <x:v>主表逐行列出七维组合、首帧提示词和对应的视频生成提示词；未通过质量门的案例不计为完成</x:v>
       </x:c>
       <x:c r="C12" s="19"/>
       <x:c r="D12" s="19"/>
@@ -1162,7 +1162,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R550bd0eb68704f4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc788de919d16403c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1253,7 +1253,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7852d4fae13847ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97508f2641814cd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>